--- a/pools-example-large-teams.xlsx
+++ b/pools-example-large-teams.xlsx
@@ -1089,130 +1089,130 @@
     <t>Victories / Points</t>
   </si>
   <si>
+    <t>Round 1 - Match 15</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 2</t>
+  </si>
+  <si>
     <t>Round 1 - Match 16</t>
   </si>
   <si>
-    <t>Round 1 - Match 2</t>
+    <t>Round 1 - Match 3</t>
   </si>
   <si>
     <t>Round 1 - Match 17</t>
   </si>
   <si>
-    <t>Round 1 - Match 3</t>
+    <t>Round 1 - Match 4</t>
   </si>
   <si>
     <t>Round 1 - Match 18</t>
   </si>
   <si>
-    <t>Round 1 - Match 4</t>
+    <t>Round 1 - Match 5</t>
   </si>
   <si>
     <t>Round 1 - Match 19</t>
   </si>
   <si>
-    <t>Round 1 - Match 5</t>
+    <t>Round 1 - Match 6</t>
   </si>
   <si>
     <t>Round 1 - Match 20</t>
   </si>
   <si>
-    <t>Round 1 - Match 6</t>
+    <t>Round 1 - Match 7</t>
   </si>
   <si>
     <t>Round 1 - Match 21</t>
   </si>
   <si>
-    <t>Round 1 - Match 7</t>
+    <t>Round 1 - Match 8</t>
   </si>
   <si>
     <t>Round 1 - Match 22</t>
   </si>
   <si>
-    <t>Round 1 - Match 8</t>
+    <t>Round 1 - Match 9</t>
   </si>
   <si>
     <t>Round 1 - Match 23</t>
   </si>
   <si>
-    <t>Round 1 - Match 9</t>
+    <t>Round 1 - Match 10</t>
   </si>
   <si>
     <t>Round 1 - Match 24</t>
   </si>
   <si>
-    <t>Round 1 - Match 10</t>
+    <t>Round 1 - Match 11</t>
   </si>
   <si>
     <t>Round 1 - Match 25</t>
   </si>
   <si>
-    <t>Round 1 - Match 11</t>
+    <t>Round 1 - Match 12</t>
   </si>
   <si>
     <t>Round 1 - Match 26</t>
   </si>
   <si>
-    <t>Round 1 - Match 12</t>
+    <t>Round 1 - Match 13</t>
   </si>
   <si>
     <t>Round 1 - Match 27</t>
   </si>
   <si>
-    <t>Round 1 - Match 13</t>
+    <t>Round 1 - Match 14</t>
   </si>
   <si>
     <t>Round 1 - Match 28</t>
   </si>
   <si>
-    <t>Round 1 - Match 14</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 29</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 15</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 30</t>
+    <t>Round 2 - Match 29</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 37</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 30</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 38</t>
   </si>
   <si>
     <t>Round 2 - Match 31</t>
   </si>
   <si>
-    <t>Round 2 - Match 38</t>
+    <t>Round 2 - Match 39</t>
   </si>
   <si>
     <t>Round 2 - Match 32</t>
   </si>
   <si>
-    <t>Round 2 - Match 39</t>
+    <t>Round 2 - Match 40</t>
   </si>
   <si>
     <t>Round 2 - Match 33</t>
   </si>
   <si>
-    <t>Round 2 - Match 40</t>
+    <t>Round 2 - Match 41</t>
   </si>
   <si>
     <t>Round 2 - Match 34</t>
   </si>
   <si>
-    <t>Round 2 - Match 41</t>
+    <t>Round 2 - Match 42</t>
   </si>
   <si>
     <t>Round 2 - Match 35</t>
   </si>
   <si>
-    <t>Round 2 - Match 42</t>
+    <t>Round 2 - Match 43</t>
   </si>
   <si>
     <t>Round 2 - Match 36</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 43</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 37</t>
   </si>
   <si>
     <t>Round 2 - Match 44</t>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="D6" s="22"/>
       <c r="E6" s="21">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -3533,7 +3533,7 @@
     <row r="8">
       <c r="A8" s="22"/>
       <c r="G8" s="21">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="21">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="20"/>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="21">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I14" s="20"/>
       <c r="K14" s="20"/>
@@ -3617,7 +3617,7 @@
         <f>data!$E$56&amp;" "&amp;data!$B$56</f>
       </c>
       <c r="G16" s="21">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="20"/>
@@ -3637,7 +3637,7 @@
       <c r="A18" s="22"/>
       <c r="D18" s="22"/>
       <c r="E18" s="21">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="20"/>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="21">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K22" s="20"/>
     </row>
@@ -3697,7 +3697,7 @@
         <f>'data'!$A$63</f>
       </c>
       <c r="G24" s="21">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K24" s="20"/>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="21">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="20"/>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="D30" s="22"/>
       <c r="E30" s="21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I30" s="20"/>
     </row>
@@ -3783,7 +3783,7 @@
         <f>data!$E$66&amp;" "&amp;data!$B$66</f>
       </c>
       <c r="G32" s="21">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="20"/>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="D34" s="22"/>
       <c r="E34" s="21">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="20"/>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="D6" s="22"/>
       <c r="E6" s="21">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -3928,7 +3928,7 @@
     <row r="8">
       <c r="A8" s="22"/>
       <c r="G8" s="21">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="21">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="20"/>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="21">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I14" s="20"/>
       <c r="K14" s="20"/>
@@ -4012,7 +4012,7 @@
         <f>data!$E$80&amp;" "&amp;data!$B$80</f>
       </c>
       <c r="G16" s="21">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="20"/>
@@ -4032,7 +4032,7 @@
       <c r="A18" s="22"/>
       <c r="D18" s="22"/>
       <c r="E18" s="21">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="20"/>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="21">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K22" s="20"/>
     </row>
@@ -4092,7 +4092,7 @@
         <f>'data'!$A$87</f>
       </c>
       <c r="G24" s="21">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K24" s="20"/>
     </row>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="21">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="20"/>
@@ -4145,18 +4145,16 @@
       <c r="A29" s="24" t="str">
         <f>'data'!$A$90</f>
       </c>
-      <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool AD-1st ",'Pool Matches'!O652)</f>
-      </c>
       <c r="I29" s="20"/>
     </row>
     <row r="30">
       <c r="A30" s="25" t="str">
         <f>data!$E$88&amp;" "&amp;data!$B$88</f>
       </c>
-      <c r="D30" s="22"/>
-      <c r="E30" s="21">
-        <v>30</v>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23" t="str">
+        <f>CONCATENATE("Pool AD-1st ",'Pool Matches'!O652)</f>
       </c>
       <c r="I30" s="20"/>
     </row>
@@ -4164,27 +4162,35 @@
       <c r="A31" s="26" t="str">
         <f>data!$E$89&amp;" "&amp;data!$B$89</f>
       </c>
-      <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G653)</f>
-      </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="20"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="20"/>
       <c r="I31" s="20"/>
     </row>
     <row r="32">
       <c r="A32" s="27" t="str">
         <f>data!$E$90&amp;" "&amp;data!$B$90</f>
       </c>
+      <c r="G32" s="21">
+        <v>44</v>
+      </c>
       <c r="H32" s="15"/>
       <c r="I32" s="20"/>
     </row>
     <row r="33">
       <c r="A33" s="22"/>
+      <c r="G33" s="20"/>
     </row>
     <row r="34">
       <c r="A34" s="24" t="str">
         <f>'data'!$A$93</f>
       </c>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23" t="str">
+        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G653)</f>
+      </c>
+      <c r="F34" s="15"/>
+      <c r="G34" s="20"/>
     </row>
     <row r="35">
       <c r="A35" s="25" t="str">
@@ -25102,289 +25108,289 @@
       </c>
       <c r="O224" s="19"/>
     </row>
-    <row r="226">
-      <c r="A226" s="13" t="s">
+    <row r="231">
+      <c r="A231" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="B226" s="13"/>
-      <c r="C226" s="13"/>
-      <c r="D226" s="13"/>
-      <c r="E226" s="13"/>
-      <c r="F226" s="13"/>
-      <c r="G226" s="13"/>
-      <c r="I226" s="13" t="s">
+      <c r="B231" s="13"/>
+      <c r="C231" s="13"/>
+      <c r="D231" s="13"/>
+      <c r="E231" s="13"/>
+      <c r="F231" s="13"/>
+      <c r="G231" s="13"/>
+      <c r="I231" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="J226" s="13"/>
-      <c r="K226" s="13"/>
-      <c r="L226" s="13"/>
-      <c r="M226" s="13"/>
-      <c r="N226" s="13"/>
-      <c r="O226" s="13"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="17" t="s">
+      <c r="J231" s="13"/>
+      <c r="K231" s="13"/>
+      <c r="L231" s="13"/>
+      <c r="M231" s="13"/>
+      <c r="N231" s="13"/>
+      <c r="O231" s="13"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="17" t="s">
         <v>330</v>
       </c>
-      <c r="D227" s="14" t="s">
+      <c r="D232" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="G227" s="16" t="s">
+      <c r="G232" s="16" t="s">
         <v>332</v>
       </c>
-      <c r="I227" s="17" t="s">
+      <c r="I232" s="17" t="s">
         <v>330</v>
       </c>
-      <c r="L227" s="14" t="s">
+      <c r="L232" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="O227" s="16" t="s">
+      <c r="O232" s="16" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="14" t="str">
-        <f>CONCATENATE("Pool AD-2nd ",'Pool Matches'!O653)</f>
-      </c>
-      <c r="B228" s="14"/>
-      <c r="C228" s="14"/>
-      <c r="D228" s="18"/>
-      <c r="E228" s="14"/>
-      <c r="F228" s="14"/>
-      <c r="G228" s="14" t="str">
-        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G652)</f>
-      </c>
-      <c r="I228" s="14" t="str">
-        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G653)</f>
-      </c>
-      <c r="J228" s="14"/>
-      <c r="K228" s="14"/>
-      <c r="L228" s="18"/>
-      <c r="M228" s="14"/>
-      <c r="N228" s="14"/>
-      <c r="O228" s="14" t="str">
-        <f>CONCATENATE("Pool AD-1st ",'Pool Matches'!O652)</f>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="14">
+    <row r="233">
+      <c r="A233" s="14" t="str">
+        <f>CONCATENATE("M 2 ",G31)</f>
+      </c>
+      <c r="B233" s="14"/>
+      <c r="C233" s="14"/>
+      <c r="D233" s="18"/>
+      <c r="E233" s="14"/>
+      <c r="F233" s="14"/>
+      <c r="G233" s="14" t="str">
+        <f>CONCATENATE("M 1 ",G15)</f>
+      </c>
+      <c r="I233" s="14" t="str">
+        <f>CONCATENATE("M 16 ",O31)</f>
+      </c>
+      <c r="J233" s="14"/>
+      <c r="K233" s="14"/>
+      <c r="L233" s="18"/>
+      <c r="M233" s="14"/>
+      <c r="N233" s="14"/>
+      <c r="O233" s="14" t="str">
+        <f>CONCATENATE("M 15 ",O15)</f>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="14">
         <v>1</v>
       </c>
-      <c r="B229" s="18"/>
-      <c r="C229" s="18"/>
-      <c r="D229" s="18"/>
-      <c r="E229" s="18"/>
-      <c r="F229" s="18"/>
-      <c r="G229" s="14">
+      <c r="B234" s="18"/>
+      <c r="C234" s="18"/>
+      <c r="D234" s="18"/>
+      <c r="E234" s="18"/>
+      <c r="F234" s="18"/>
+      <c r="G234" s="14">
         <v>1</v>
       </c>
-      <c r="I229" s="14">
+      <c r="I234" s="14">
         <v>1</v>
       </c>
-      <c r="J229" s="18"/>
-      <c r="K229" s="18"/>
-      <c r="L229" s="18"/>
-      <c r="M229" s="18"/>
-      <c r="N229" s="18"/>
-      <c r="O229" s="14">
+      <c r="J234" s="18"/>
+      <c r="K234" s="18"/>
+      <c r="L234" s="18"/>
+      <c r="M234" s="18"/>
+      <c r="N234" s="18"/>
+      <c r="O234" s="14">
         <v>1</v>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="14">
+    <row r="235">
+      <c r="A235" s="14">
         <v>2</v>
       </c>
-      <c r="B230" s="18"/>
-      <c r="C230" s="18"/>
-      <c r="D230" s="18"/>
-      <c r="E230" s="18"/>
-      <c r="F230" s="18"/>
-      <c r="G230" s="14">
+      <c r="B235" s="18"/>
+      <c r="C235" s="18"/>
+      <c r="D235" s="18"/>
+      <c r="E235" s="18"/>
+      <c r="F235" s="18"/>
+      <c r="G235" s="14">
         <v>2</v>
       </c>
-      <c r="I230" s="14">
+      <c r="I235" s="14">
         <v>2</v>
       </c>
-      <c r="J230" s="18"/>
-      <c r="K230" s="18"/>
-      <c r="L230" s="18"/>
-      <c r="M230" s="18"/>
-      <c r="N230" s="18"/>
-      <c r="O230" s="14">
+      <c r="J235" s="18"/>
+      <c r="K235" s="18"/>
+      <c r="L235" s="18"/>
+      <c r="M235" s="18"/>
+      <c r="N235" s="18"/>
+      <c r="O235" s="14">
         <v>2</v>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="14">
+    <row r="236">
+      <c r="A236" s="14">
         <v>3</v>
       </c>
-      <c r="B231" s="18"/>
-      <c r="C231" s="18"/>
-      <c r="D231" s="18"/>
-      <c r="E231" s="18"/>
-      <c r="F231" s="18"/>
-      <c r="G231" s="14">
+      <c r="B236" s="18"/>
+      <c r="C236" s="18"/>
+      <c r="D236" s="18"/>
+      <c r="E236" s="18"/>
+      <c r="F236" s="18"/>
+      <c r="G236" s="14">
         <v>3</v>
       </c>
-      <c r="I231" s="14">
+      <c r="I236" s="14">
         <v>3</v>
       </c>
-      <c r="J231" s="18"/>
-      <c r="K231" s="18"/>
-      <c r="L231" s="18"/>
-      <c r="M231" s="18"/>
-      <c r="N231" s="18"/>
-      <c r="O231" s="14">
+      <c r="J236" s="18"/>
+      <c r="K236" s="18"/>
+      <c r="L236" s="18"/>
+      <c r="M236" s="18"/>
+      <c r="N236" s="18"/>
+      <c r="O236" s="14">
         <v>3</v>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="14">
+    <row r="237">
+      <c r="A237" s="14">
         <v>4</v>
       </c>
-      <c r="B232" s="18"/>
-      <c r="C232" s="18"/>
-      <c r="D232" s="18"/>
-      <c r="E232" s="18"/>
-      <c r="F232" s="18"/>
-      <c r="G232" s="14">
+      <c r="B237" s="18"/>
+      <c r="C237" s="18"/>
+      <c r="D237" s="18"/>
+      <c r="E237" s="18"/>
+      <c r="F237" s="18"/>
+      <c r="G237" s="14">
         <v>4</v>
       </c>
-      <c r="I232" s="14">
+      <c r="I237" s="14">
         <v>4</v>
       </c>
-      <c r="J232" s="18"/>
-      <c r="K232" s="18"/>
-      <c r="L232" s="18"/>
-      <c r="M232" s="18"/>
-      <c r="N232" s="18"/>
-      <c r="O232" s="14">
+      <c r="J237" s="18"/>
+      <c r="K237" s="18"/>
+      <c r="L237" s="18"/>
+      <c r="M237" s="18"/>
+      <c r="N237" s="18"/>
+      <c r="O237" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="14">
-        <v>5</v>
-      </c>
-      <c r="B233" s="18"/>
-      <c r="C233" s="18"/>
-      <c r="D233" s="18"/>
-      <c r="E233" s="18"/>
-      <c r="F233" s="18"/>
-      <c r="G233" s="14">
-        <v>5</v>
-      </c>
-      <c r="I233" s="14">
-        <v>5</v>
-      </c>
-      <c r="J233" s="18"/>
-      <c r="K233" s="18"/>
-      <c r="L233" s="18"/>
-      <c r="M233" s="18"/>
-      <c r="N233" s="18"/>
-      <c r="O233" s="14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="14" t="str">
-        <f>CONCATENATE("Pool AD-2nd ",'Pool Matches'!O653)</f>
-      </c>
-      <c r="B235" s="14" t="s">
+    <row r="238">
+      <c r="A238" s="14">
+        <v>5</v>
+      </c>
+      <c r="B238" s="18"/>
+      <c r="C238" s="18"/>
+      <c r="D238" s="18"/>
+      <c r="E238" s="18"/>
+      <c r="F238" s="18"/>
+      <c r="G238" s="14">
+        <v>5</v>
+      </c>
+      <c r="I238" s="14">
+        <v>5</v>
+      </c>
+      <c r="J238" s="18"/>
+      <c r="K238" s="18"/>
+      <c r="L238" s="18"/>
+      <c r="M238" s="18"/>
+      <c r="N238" s="18"/>
+      <c r="O238" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="14" t="str">
+        <f>CONCATENATE("M 2 ",G31)</f>
+      </c>
+      <c r="B240" s="14" t="s">
         <v>338</v>
       </c>
-      <c r="C235" s="14" t="s">
+      <c r="C240" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="D235" s="14"/>
-      <c r="E235" s="14" t="s">
+      <c r="D240" s="14"/>
+      <c r="E240" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="F235" s="14" t="s">
+      <c r="F240" s="14" t="s">
         <v>338</v>
       </c>
-      <c r="G235" s="14" t="str">
-        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G652)</f>
-      </c>
-      <c r="I235" s="14" t="str">
-        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G653)</f>
-      </c>
-      <c r="J235" s="14" t="s">
+      <c r="G240" s="14" t="str">
+        <f>CONCATENATE("M 1 ",G15)</f>
+      </c>
+      <c r="I240" s="14" t="str">
+        <f>CONCATENATE("M 16 ",O31)</f>
+      </c>
+      <c r="J240" s="14" t="s">
         <v>338</v>
       </c>
-      <c r="K235" s="14" t="s">
+      <c r="K240" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="L235" s="14"/>
-      <c r="M235" s="14" t="s">
+      <c r="L240" s="14"/>
+      <c r="M240" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="N235" s="14" t="s">
+      <c r="N240" s="14" t="s">
         <v>338</v>
       </c>
-      <c r="O235" s="14" t="str">
-        <f>CONCATENATE("Pool AD-1st ",'Pool Matches'!O652)</f>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="14" t="s">
+      <c r="O240" s="14" t="str">
+        <f>CONCATENATE("M 15 ",O15)</f>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="14" t="s">
         <v>349</v>
       </c>
-      <c r="B236" s="14" t="str">
-        <f>IF(UPPER(D229)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C229," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F229," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D233)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C233," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F233," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="C236" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C233," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="D236" s="14"/>
-      <c r="E236" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F233," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F236" s="14" t="str">
-        <f>IF(UPPER(D229)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F229," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C229," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D233)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F233," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C233," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="G236" s="14" t="s">
+      <c r="B241" s="14" t="str">
+        <f>IF(UPPER(D234)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C234," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F234," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D235)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B235," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C235," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E235," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F235," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D236)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C236," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F236," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D237)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C237," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F237," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-",""))),1,0))</f>
+      </c>
+      <c r="C241" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B235," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C235," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="D241" s="14"/>
+      <c r="E241" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E235," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F235," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F241" s="14" t="str">
+        <f>IF(UPPER(D234)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F234," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C234," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D235)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E235," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F235," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B235," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C235," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D236)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F236," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C236," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D237)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F237," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C237," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-",""))),1,0))</f>
+      </c>
+      <c r="G241" s="14" t="s">
         <v>349</v>
       </c>
-      <c r="I236" s="14" t="s">
+      <c r="I241" s="14" t="s">
         <v>349</v>
       </c>
-      <c r="J236" s="14" t="str">
-        <f>IF(UPPER(L229)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K229," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N229," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L233)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K233," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N233," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="K236" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K233," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="L236" s="14"/>
-      <c r="M236" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N233," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="N236" s="14" t="str">
-        <f>IF(UPPER(L229)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N229," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K229," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L233)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N233," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K233," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="O236" s="14" t="s">
+      <c r="J241" s="14" t="str">
+        <f>IF(UPPER(L234)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K234," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N234," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L235)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J235," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K235," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M235," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N235," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L236)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K236," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N236," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L237)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K237," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N237," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-",""))),1,0))</f>
+      </c>
+      <c r="K241" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J235," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K235," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="L241" s="14"/>
+      <c r="M241" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M235," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N235," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N241" s="14" t="str">
+        <f>IF(UPPER(L234)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N234," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K234," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L235)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M235," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N235," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J235," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K235," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L236)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N236," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K236," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L237)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N237," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K237," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-",""))),1,0))</f>
+      </c>
+      <c r="O241" s="14" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="239">
-      <c r="F239" t="s">
+    <row r="244">
+      <c r="F244" t="s">
         <v>344</v>
       </c>
-      <c r="G239" s="19"/>
-      <c r="N239" t="s">
+      <c r="G244" s="19"/>
+      <c r="N244" t="s">
         <v>344</v>
       </c>
-      <c r="O239" s="19"/>
-    </row>
-    <row r="240">
-      <c r="F240" t="s">
+      <c r="O244" s="19"/>
+    </row>
+    <row r="245">
+      <c r="F245" t="s">
         <v>345</v>
       </c>
-      <c r="G240" s="19"/>
-      <c r="N240" t="s">
+      <c r="G245" s="19"/>
+      <c r="N245" t="s">
         <v>345</v>
       </c>
-      <c r="O240" s="19"/>
+      <c r="O245" s="19"/>
     </row>
     <row r="247">
       <c r="A247" s="13" t="s">
@@ -25428,7 +25434,7 @@
     </row>
     <row r="249">
       <c r="A249" s="14" t="str">
-        <f>CONCATENATE("M 2 ",G31)</f>
+        <f>CONCATENATE("M 4 ",G63)</f>
       </c>
       <c r="B249" s="14"/>
       <c r="C249" s="14"/>
@@ -25436,10 +25442,10 @@
       <c r="E249" s="14"/>
       <c r="F249" s="14"/>
       <c r="G249" s="14" t="str">
-        <f>CONCATENATE("M 1 ",G15)</f>
+        <f>CONCATENATE("M 3 ",G47)</f>
       </c>
       <c r="I249" s="14" t="str">
-        <f>CONCATENATE("M 17 ",O31)</f>
+        <f>CONCATENATE("M 18 ",O63)</f>
       </c>
       <c r="J249" s="14"/>
       <c r="K249" s="14"/>
@@ -25447,7 +25453,7 @@
       <c r="M249" s="14"/>
       <c r="N249" s="14"/>
       <c r="O249" s="14" t="str">
-        <f>CONCATENATE("M 16 ",O15)</f>
+        <f>CONCATENATE("M 17 ",O47)</f>
       </c>
     </row>
     <row r="250">
@@ -25572,7 +25578,7 @@
     </row>
     <row r="256">
       <c r="A256" s="14" t="str">
-        <f>CONCATENATE("M 2 ",G31)</f>
+        <f>CONCATENATE("M 4 ",G63)</f>
       </c>
       <c r="B256" s="14" t="s">
         <v>338</v>
@@ -25588,10 +25594,10 @@
         <v>338</v>
       </c>
       <c r="G256" s="14" t="str">
-        <f>CONCATENATE("M 1 ",G15)</f>
+        <f>CONCATENATE("M 3 ",G47)</f>
       </c>
       <c r="I256" s="14" t="str">
-        <f>CONCATENATE("M 17 ",O31)</f>
+        <f>CONCATENATE("M 18 ",O63)</f>
       </c>
       <c r="J256" s="14" t="s">
         <v>338</v>
@@ -25607,7 +25613,7 @@
         <v>338</v>
       </c>
       <c r="O256" s="14" t="str">
-        <f>CONCATENATE("M 16 ",O15)</f>
+        <f>CONCATENATE("M 17 ",O47)</f>
       </c>
     </row>
     <row r="257">
@@ -25712,7 +25718,7 @@
     </row>
     <row r="265">
       <c r="A265" s="14" t="str">
-        <f>CONCATENATE("M 4 ",G63)</f>
+        <f>CONCATENATE("M 6 ",G95)</f>
       </c>
       <c r="B265" s="14"/>
       <c r="C265" s="14"/>
@@ -25720,10 +25726,10 @@
       <c r="E265" s="14"/>
       <c r="F265" s="14"/>
       <c r="G265" s="14" t="str">
-        <f>CONCATENATE("M 3 ",G47)</f>
+        <f>CONCATENATE("M 5 ",G79)</f>
       </c>
       <c r="I265" s="14" t="str">
-        <f>CONCATENATE("M 19 ",O63)</f>
+        <f>CONCATENATE("M 20 ",O95)</f>
       </c>
       <c r="J265" s="14"/>
       <c r="K265" s="14"/>
@@ -25731,7 +25737,7 @@
       <c r="M265" s="14"/>
       <c r="N265" s="14"/>
       <c r="O265" s="14" t="str">
-        <f>CONCATENATE("M 18 ",O47)</f>
+        <f>CONCATENATE("M 19 ",O79)</f>
       </c>
     </row>
     <row r="266">
@@ -25856,7 +25862,7 @@
     </row>
     <row r="272">
       <c r="A272" s="14" t="str">
-        <f>CONCATENATE("M 4 ",G63)</f>
+        <f>CONCATENATE("M 6 ",G95)</f>
       </c>
       <c r="B272" s="14" t="s">
         <v>338</v>
@@ -25872,10 +25878,10 @@
         <v>338</v>
       </c>
       <c r="G272" s="14" t="str">
-        <f>CONCATENATE("M 3 ",G47)</f>
+        <f>CONCATENATE("M 5 ",G79)</f>
       </c>
       <c r="I272" s="14" t="str">
-        <f>CONCATENATE("M 19 ",O63)</f>
+        <f>CONCATENATE("M 20 ",O95)</f>
       </c>
       <c r="J272" s="14" t="s">
         <v>338</v>
@@ -25891,7 +25897,7 @@
         <v>338</v>
       </c>
       <c r="O272" s="14" t="str">
-        <f>CONCATENATE("M 18 ",O47)</f>
+        <f>CONCATENATE("M 19 ",O79)</f>
       </c>
     </row>
     <row r="273">
@@ -25996,7 +26002,7 @@
     </row>
     <row r="281">
       <c r="A281" s="14" t="str">
-        <f>CONCATENATE("M 6 ",G95)</f>
+        <f>CONCATENATE("M 8 ",G127)</f>
       </c>
       <c r="B281" s="14"/>
       <c r="C281" s="14"/>
@@ -26004,10 +26010,10 @@
       <c r="E281" s="14"/>
       <c r="F281" s="14"/>
       <c r="G281" s="14" t="str">
-        <f>CONCATENATE("M 5 ",G79)</f>
+        <f>CONCATENATE("M 7 ",G111)</f>
       </c>
       <c r="I281" s="14" t="str">
-        <f>CONCATENATE("M 21 ",O95)</f>
+        <f>CONCATENATE("M 22 ",O127)</f>
       </c>
       <c r="J281" s="14"/>
       <c r="K281" s="14"/>
@@ -26015,7 +26021,7 @@
       <c r="M281" s="14"/>
       <c r="N281" s="14"/>
       <c r="O281" s="14" t="str">
-        <f>CONCATENATE("M 20 ",O79)</f>
+        <f>CONCATENATE("M 21 ",O111)</f>
       </c>
     </row>
     <row r="282">
@@ -26140,7 +26146,7 @@
     </row>
     <row r="288">
       <c r="A288" s="14" t="str">
-        <f>CONCATENATE("M 6 ",G95)</f>
+        <f>CONCATENATE("M 8 ",G127)</f>
       </c>
       <c r="B288" s="14" t="s">
         <v>338</v>
@@ -26156,10 +26162,10 @@
         <v>338</v>
       </c>
       <c r="G288" s="14" t="str">
-        <f>CONCATENATE("M 5 ",G79)</f>
+        <f>CONCATENATE("M 7 ",G111)</f>
       </c>
       <c r="I288" s="14" t="str">
-        <f>CONCATENATE("M 21 ",O95)</f>
+        <f>CONCATENATE("M 22 ",O127)</f>
       </c>
       <c r="J288" s="14" t="s">
         <v>338</v>
@@ -26175,7 +26181,7 @@
         <v>338</v>
       </c>
       <c r="O288" s="14" t="str">
-        <f>CONCATENATE("M 20 ",O79)</f>
+        <f>CONCATENATE("M 21 ",O111)</f>
       </c>
     </row>
     <row r="289">
@@ -26280,7 +26286,7 @@
     </row>
     <row r="297">
       <c r="A297" s="14" t="str">
-        <f>CONCATENATE("M 8 ",G127)</f>
+        <f>CONCATENATE("M 10 ",G159)</f>
       </c>
       <c r="B297" s="14"/>
       <c r="C297" s="14"/>
@@ -26288,10 +26294,10 @@
       <c r="E297" s="14"/>
       <c r="F297" s="14"/>
       <c r="G297" s="14" t="str">
-        <f>CONCATENATE("M 7 ",G111)</f>
+        <f>CONCATENATE("M 9 ",G143)</f>
       </c>
       <c r="I297" s="14" t="str">
-        <f>CONCATENATE("M 23 ",O127)</f>
+        <f>CONCATENATE("M 24 ",O159)</f>
       </c>
       <c r="J297" s="14"/>
       <c r="K297" s="14"/>
@@ -26299,7 +26305,7 @@
       <c r="M297" s="14"/>
       <c r="N297" s="14"/>
       <c r="O297" s="14" t="str">
-        <f>CONCATENATE("M 22 ",O111)</f>
+        <f>CONCATENATE("M 23 ",O143)</f>
       </c>
     </row>
     <row r="298">
@@ -26424,7 +26430,7 @@
     </row>
     <row r="304">
       <c r="A304" s="14" t="str">
-        <f>CONCATENATE("M 8 ",G127)</f>
+        <f>CONCATENATE("M 10 ",G159)</f>
       </c>
       <c r="B304" s="14" t="s">
         <v>338</v>
@@ -26440,10 +26446,10 @@
         <v>338</v>
       </c>
       <c r="G304" s="14" t="str">
-        <f>CONCATENATE("M 7 ",G111)</f>
+        <f>CONCATENATE("M 9 ",G143)</f>
       </c>
       <c r="I304" s="14" t="str">
-        <f>CONCATENATE("M 23 ",O127)</f>
+        <f>CONCATENATE("M 24 ",O159)</f>
       </c>
       <c r="J304" s="14" t="s">
         <v>338</v>
@@ -26459,7 +26465,7 @@
         <v>338</v>
       </c>
       <c r="O304" s="14" t="str">
-        <f>CONCATENATE("M 22 ",O111)</f>
+        <f>CONCATENATE("M 23 ",O143)</f>
       </c>
     </row>
     <row r="305">
@@ -26564,7 +26570,7 @@
     </row>
     <row r="313">
       <c r="A313" s="14" t="str">
-        <f>CONCATENATE("M 10 ",G159)</f>
+        <f>CONCATENATE("M 12 ",G191)</f>
       </c>
       <c r="B313" s="14"/>
       <c r="C313" s="14"/>
@@ -26572,10 +26578,10 @@
       <c r="E313" s="14"/>
       <c r="F313" s="14"/>
       <c r="G313" s="14" t="str">
-        <f>CONCATENATE("M 9 ",G143)</f>
+        <f>CONCATENATE("M 11 ",G175)</f>
       </c>
       <c r="I313" s="14" t="str">
-        <f>CONCATENATE("M 25 ",O159)</f>
+        <f>CONCATENATE("M 26 ",O191)</f>
       </c>
       <c r="J313" s="14"/>
       <c r="K313" s="14"/>
@@ -26583,7 +26589,7 @@
       <c r="M313" s="14"/>
       <c r="N313" s="14"/>
       <c r="O313" s="14" t="str">
-        <f>CONCATENATE("M 24 ",O143)</f>
+        <f>CONCATENATE("M 25 ",O175)</f>
       </c>
     </row>
     <row r="314">
@@ -26708,7 +26714,7 @@
     </row>
     <row r="320">
       <c r="A320" s="14" t="str">
-        <f>CONCATENATE("M 10 ",G159)</f>
+        <f>CONCATENATE("M 12 ",G191)</f>
       </c>
       <c r="B320" s="14" t="s">
         <v>338</v>
@@ -26724,10 +26730,10 @@
         <v>338</v>
       </c>
       <c r="G320" s="14" t="str">
-        <f>CONCATENATE("M 9 ",G143)</f>
+        <f>CONCATENATE("M 11 ",G175)</f>
       </c>
       <c r="I320" s="14" t="str">
-        <f>CONCATENATE("M 25 ",O159)</f>
+        <f>CONCATENATE("M 26 ",O191)</f>
       </c>
       <c r="J320" s="14" t="s">
         <v>338</v>
@@ -26743,7 +26749,7 @@
         <v>338</v>
       </c>
       <c r="O320" s="14" t="str">
-        <f>CONCATENATE("M 24 ",O143)</f>
+        <f>CONCATENATE("M 25 ",O175)</f>
       </c>
     </row>
     <row r="321">
@@ -26848,7 +26854,7 @@
     </row>
     <row r="329">
       <c r="A329" s="14" t="str">
-        <f>CONCATENATE("M 12 ",G191)</f>
+        <f>CONCATENATE("M 14 ",G223)</f>
       </c>
       <c r="B329" s="14"/>
       <c r="C329" s="14"/>
@@ -26856,10 +26862,10 @@
       <c r="E329" s="14"/>
       <c r="F329" s="14"/>
       <c r="G329" s="14" t="str">
-        <f>CONCATENATE("M 11 ",G175)</f>
+        <f>CONCATENATE("M 13 ",G207)</f>
       </c>
       <c r="I329" s="14" t="str">
-        <f>CONCATENATE("M 27 ",O191)</f>
+        <f>CONCATENATE("M 28 ",O223)</f>
       </c>
       <c r="J329" s="14"/>
       <c r="K329" s="14"/>
@@ -26867,7 +26873,7 @@
       <c r="M329" s="14"/>
       <c r="N329" s="14"/>
       <c r="O329" s="14" t="str">
-        <f>CONCATENATE("M 26 ",O175)</f>
+        <f>CONCATENATE("M 27 ",O207)</f>
       </c>
     </row>
     <row r="330">
@@ -26992,7 +26998,7 @@
     </row>
     <row r="336">
       <c r="A336" s="14" t="str">
-        <f>CONCATENATE("M 12 ",G191)</f>
+        <f>CONCATENATE("M 14 ",G223)</f>
       </c>
       <c r="B336" s="14" t="s">
         <v>338</v>
@@ -27008,10 +27014,10 @@
         <v>338</v>
       </c>
       <c r="G336" s="14" t="str">
-        <f>CONCATENATE("M 11 ",G175)</f>
+        <f>CONCATENATE("M 13 ",G207)</f>
       </c>
       <c r="I336" s="14" t="str">
-        <f>CONCATENATE("M 27 ",O191)</f>
+        <f>CONCATENATE("M 28 ",O223)</f>
       </c>
       <c r="J336" s="14" t="s">
         <v>338</v>
@@ -27027,7 +27033,7 @@
         <v>338</v>
       </c>
       <c r="O336" s="14" t="str">
-        <f>CONCATENATE("M 26 ",O175)</f>
+        <f>CONCATENATE("M 27 ",O207)</f>
       </c>
     </row>
     <row r="337">
@@ -27132,7 +27138,7 @@
     </row>
     <row r="345">
       <c r="A345" s="14" t="str">
-        <f>CONCATENATE("M 14 ",G223)</f>
+        <f>CONCATENATE("Pool AD-2nd ",'Pool Matches'!O653)</f>
       </c>
       <c r="B345" s="14"/>
       <c r="C345" s="14"/>
@@ -27140,10 +27146,10 @@
       <c r="E345" s="14"/>
       <c r="F345" s="14"/>
       <c r="G345" s="14" t="str">
-        <f>CONCATENATE("M 13 ",G207)</f>
+        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G652)</f>
       </c>
       <c r="I345" s="14" t="str">
-        <f>CONCATENATE("M 29 ",O223)</f>
+        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G653)</f>
       </c>
       <c r="J345" s="14"/>
       <c r="K345" s="14"/>
@@ -27151,7 +27157,7 @@
       <c r="M345" s="14"/>
       <c r="N345" s="14"/>
       <c r="O345" s="14" t="str">
-        <f>CONCATENATE("M 28 ",O207)</f>
+        <f>CONCATENATE("Pool AD-1st ",'Pool Matches'!O652)</f>
       </c>
     </row>
     <row r="346">
@@ -27276,7 +27282,7 @@
     </row>
     <row r="352">
       <c r="A352" s="14" t="str">
-        <f>CONCATENATE("M 14 ",G223)</f>
+        <f>CONCATENATE("Pool AD-2nd ",'Pool Matches'!O653)</f>
       </c>
       <c r="B352" s="14" t="s">
         <v>338</v>
@@ -27292,10 +27298,10 @@
         <v>338</v>
       </c>
       <c r="G352" s="14" t="str">
-        <f>CONCATENATE("M 13 ",G207)</f>
+        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G652)</f>
       </c>
       <c r="I352" s="14" t="str">
-        <f>CONCATENATE("M 29 ",O223)</f>
+        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G653)</f>
       </c>
       <c r="J352" s="14" t="s">
         <v>338</v>
@@ -27311,7 +27317,7 @@
         <v>338</v>
       </c>
       <c r="O352" s="14" t="str">
-        <f>CONCATENATE("M 28 ",O207)</f>
+        <f>CONCATENATE("Pool AD-1st ",'Pool Matches'!O652)</f>
       </c>
     </row>
     <row r="353">
@@ -27416,7 +27422,7 @@
     </row>
     <row r="366">
       <c r="A366" s="14" t="str">
-        <f>CONCATENATE("M 32 ",G276)</f>
+        <f>CONCATENATE("M 30 ",G260)</f>
       </c>
       <c r="B366" s="14"/>
       <c r="C366" s="14"/>
@@ -27424,10 +27430,10 @@
       <c r="E366" s="14"/>
       <c r="F366" s="14"/>
       <c r="G366" s="14" t="str">
-        <f>CONCATENATE("M 31 ",G260)</f>
+        <f>CONCATENATE("M 29 ",G244)</f>
       </c>
       <c r="I366" s="14" t="str">
-        <f>CONCATENATE("M 39 ",O276)</f>
+        <f>CONCATENATE("M 38 ",O260)</f>
       </c>
       <c r="J366" s="14"/>
       <c r="K366" s="14"/>
@@ -27435,7 +27441,7 @@
       <c r="M366" s="14"/>
       <c r="N366" s="14"/>
       <c r="O366" s="14" t="str">
-        <f>CONCATENATE("M 38 ",O260)</f>
+        <f>CONCATENATE("M 37 ",O244)</f>
       </c>
     </row>
     <row r="367">
@@ -27560,7 +27566,7 @@
     </row>
     <row r="373">
       <c r="A373" s="14" t="str">
-        <f>CONCATENATE("M 32 ",G276)</f>
+        <f>CONCATENATE("M 30 ",G260)</f>
       </c>
       <c r="B373" s="14" t="s">
         <v>338</v>
@@ -27576,10 +27582,10 @@
         <v>338</v>
       </c>
       <c r="G373" s="14" t="str">
-        <f>CONCATENATE("M 31 ",G260)</f>
+        <f>CONCATENATE("M 29 ",G244)</f>
       </c>
       <c r="I373" s="14" t="str">
-        <f>CONCATENATE("M 39 ",O276)</f>
+        <f>CONCATENATE("M 38 ",O260)</f>
       </c>
       <c r="J373" s="14" t="s">
         <v>338</v>
@@ -27595,7 +27601,7 @@
         <v>338</v>
       </c>
       <c r="O373" s="14" t="str">
-        <f>CONCATENATE("M 38 ",O260)</f>
+        <f>CONCATENATE("M 37 ",O244)</f>
       </c>
     </row>
     <row r="374">
@@ -27700,7 +27706,7 @@
     </row>
     <row r="382">
       <c r="A382" s="14" t="str">
-        <f>CONCATENATE("M 34 ",G308)</f>
+        <f>CONCATENATE("M 32 ",G292)</f>
       </c>
       <c r="B382" s="14"/>
       <c r="C382" s="14"/>
@@ -27708,10 +27714,10 @@
       <c r="E382" s="14"/>
       <c r="F382" s="14"/>
       <c r="G382" s="14" t="str">
-        <f>CONCATENATE("M 33 ",G292)</f>
+        <f>CONCATENATE("M 31 ",G276)</f>
       </c>
       <c r="I382" s="14" t="str">
-        <f>CONCATENATE("M 41 ",O308)</f>
+        <f>CONCATENATE("M 40 ",O292)</f>
       </c>
       <c r="J382" s="14"/>
       <c r="K382" s="14"/>
@@ -27719,7 +27725,7 @@
       <c r="M382" s="14"/>
       <c r="N382" s="14"/>
       <c r="O382" s="14" t="str">
-        <f>CONCATENATE("M 40 ",O292)</f>
+        <f>CONCATENATE("M 39 ",O276)</f>
       </c>
     </row>
     <row r="383">
@@ -27844,7 +27850,7 @@
     </row>
     <row r="389">
       <c r="A389" s="14" t="str">
-        <f>CONCATENATE("M 34 ",G308)</f>
+        <f>CONCATENATE("M 32 ",G292)</f>
       </c>
       <c r="B389" s="14" t="s">
         <v>338</v>
@@ -27860,10 +27866,10 @@
         <v>338</v>
       </c>
       <c r="G389" s="14" t="str">
-        <f>CONCATENATE("M 33 ",G292)</f>
+        <f>CONCATENATE("M 31 ",G276)</f>
       </c>
       <c r="I389" s="14" t="str">
-        <f>CONCATENATE("M 41 ",O308)</f>
+        <f>CONCATENATE("M 40 ",O292)</f>
       </c>
       <c r="J389" s="14" t="s">
         <v>338</v>
@@ -27879,7 +27885,7 @@
         <v>338</v>
       </c>
       <c r="O389" s="14" t="str">
-        <f>CONCATENATE("M 40 ",O292)</f>
+        <f>CONCATENATE("M 39 ",O276)</f>
       </c>
     </row>
     <row r="390">
@@ -27984,7 +27990,7 @@
     </row>
     <row r="398">
       <c r="A398" s="14" t="str">
-        <f>CONCATENATE("M 36 ",G340)</f>
+        <f>CONCATENATE("M 34 ",G324)</f>
       </c>
       <c r="B398" s="14"/>
       <c r="C398" s="14"/>
@@ -27992,10 +27998,10 @@
       <c r="E398" s="14"/>
       <c r="F398" s="14"/>
       <c r="G398" s="14" t="str">
-        <f>CONCATENATE("M 35 ",G324)</f>
+        <f>CONCATENATE("M 33 ",G308)</f>
       </c>
       <c r="I398" s="14" t="str">
-        <f>CONCATENATE("M 43 ",O340)</f>
+        <f>CONCATENATE("M 42 ",O324)</f>
       </c>
       <c r="J398" s="14"/>
       <c r="K398" s="14"/>
@@ -28003,7 +28009,7 @@
       <c r="M398" s="14"/>
       <c r="N398" s="14"/>
       <c r="O398" s="14" t="str">
-        <f>CONCATENATE("M 42 ",O324)</f>
+        <f>CONCATENATE("M 41 ",O308)</f>
       </c>
     </row>
     <row r="399">
@@ -28128,7 +28134,7 @@
     </row>
     <row r="405">
       <c r="A405" s="14" t="str">
-        <f>CONCATENATE("M 36 ",G340)</f>
+        <f>CONCATENATE("M 34 ",G324)</f>
       </c>
       <c r="B405" s="14" t="s">
         <v>338</v>
@@ -28144,10 +28150,10 @@
         <v>338</v>
       </c>
       <c r="G405" s="14" t="str">
-        <f>CONCATENATE("M 35 ",G324)</f>
+        <f>CONCATENATE("M 33 ",G308)</f>
       </c>
       <c r="I405" s="14" t="str">
-        <f>CONCATENATE("M 43 ",O340)</f>
+        <f>CONCATENATE("M 42 ",O324)</f>
       </c>
       <c r="J405" s="14" t="s">
         <v>338</v>
@@ -28163,7 +28169,7 @@
         <v>338</v>
       </c>
       <c r="O405" s="14" t="str">
-        <f>CONCATENATE("M 42 ",O324)</f>
+        <f>CONCATENATE("M 41 ",O308)</f>
       </c>
     </row>
     <row r="406">
@@ -28268,7 +28274,7 @@
     </row>
     <row r="414">
       <c r="A414" s="14" t="str">
-        <f>CONCATENATE("M 15 ",G239)</f>
+        <f>CONCATENATE("M 36 ",G356)</f>
       </c>
       <c r="B414" s="14"/>
       <c r="C414" s="14"/>
@@ -28276,10 +28282,10 @@
       <c r="E414" s="14"/>
       <c r="F414" s="14"/>
       <c r="G414" s="14" t="str">
-        <f>CONCATENATE("M 37 ",G356)</f>
+        <f>CONCATENATE("M 35 ",G340)</f>
       </c>
       <c r="I414" s="14" t="str">
-        <f>CONCATENATE("M 30 ",O239)</f>
+        <f>CONCATENATE("M 44 ",O356)</f>
       </c>
       <c r="J414" s="14"/>
       <c r="K414" s="14"/>
@@ -28287,7 +28293,7 @@
       <c r="M414" s="14"/>
       <c r="N414" s="14"/>
       <c r="O414" s="14" t="str">
-        <f>CONCATENATE("M 44 ",O356)</f>
+        <f>CONCATENATE("M 43 ",O340)</f>
       </c>
     </row>
     <row r="415">
@@ -28412,7 +28418,7 @@
     </row>
     <row r="421">
       <c r="A421" s="14" t="str">
-        <f>CONCATENATE("M 15 ",G239)</f>
+        <f>CONCATENATE("M 36 ",G356)</f>
       </c>
       <c r="B421" s="14" t="s">
         <v>338</v>
@@ -28428,10 +28434,10 @@
         <v>338</v>
       </c>
       <c r="G421" s="14" t="str">
-        <f>CONCATENATE("M 37 ",G356)</f>
+        <f>CONCATENATE("M 35 ",G340)</f>
       </c>
       <c r="I421" s="14" t="str">
-        <f>CONCATENATE("M 30 ",O239)</f>
+        <f>CONCATENATE("M 44 ",O356)</f>
       </c>
       <c r="J421" s="14" t="s">
         <v>338</v>
@@ -28447,7 +28453,7 @@
         <v>338</v>
       </c>
       <c r="O421" s="14" t="str">
-        <f>CONCATENATE("M 44 ",O356)</f>
+        <f>CONCATENATE("M 43 ",O340)</f>
       </c>
     </row>
     <row r="422">
@@ -29549,8 +29555,8 @@
     <mergeCell ref="I194:O194"/>
     <mergeCell ref="A210:G210"/>
     <mergeCell ref="I210:O210"/>
-    <mergeCell ref="A226:G226"/>
-    <mergeCell ref="I226:O226"/>
+    <mergeCell ref="A231:G231"/>
+    <mergeCell ref="I231:O231"/>
     <mergeCell ref="A247:G247"/>
     <mergeCell ref="I247:O247"/>
     <mergeCell ref="A263:G263"/>
@@ -29590,7 +29596,7 @@
     <brk id="129" max="16383" man="true"/>
     <brk id="161" max="16383" man="true"/>
     <brk id="193" max="16383" man="true"/>
-    <brk id="225" max="16383" man="true"/>
+    <brk id="230" max="16383" man="true"/>
     <brk id="262" max="16383" man="true"/>
     <brk id="294" max="16383" man="true"/>
     <brk id="326" max="16383" man="true"/>
@@ -29673,7 +29679,7 @@
         <f>data!$E$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="G8" s="21">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -29755,7 +29761,7 @@
         <f>data!$E$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="G16" s="21">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="20"/>
@@ -29835,7 +29841,7 @@
     <row r="24">
       <c r="A24" s="22"/>
       <c r="G24" s="21">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K24" s="20"/>
     </row>
@@ -29921,7 +29927,7 @@
         <f>data!$E$20&amp;" "&amp;data!$B$20</f>
       </c>
       <c r="G32" s="21">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="20"/>
@@ -30071,7 +30077,7 @@
     <row r="8">
       <c r="A8" s="22"/>
       <c r="G8" s="21">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
@@ -30155,7 +30161,7 @@
         <f>data!$E$35&amp;" "&amp;data!$B$35</f>
       </c>
       <c r="G16" s="21">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="20"/>
@@ -30235,7 +30241,7 @@
         <f>'data'!$A$42</f>
       </c>
       <c r="G24" s="21">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K24" s="20"/>
     </row>
@@ -30288,18 +30294,16 @@
       <c r="A29" s="24" t="str">
         <f>'data'!$A$45</f>
       </c>
-      <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G652)</f>
-      </c>
       <c r="I29" s="20"/>
     </row>
     <row r="30">
       <c r="A30" s="25" t="str">
         <f>data!$E$43&amp;" "&amp;data!$B$43</f>
       </c>
-      <c r="D30" s="22"/>
-      <c r="E30" s="21">
-        <v>15</v>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23" t="str">
+        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G652)</f>
       </c>
       <c r="I30" s="20"/>
     </row>
@@ -30307,27 +30311,35 @@
       <c r="A31" s="26" t="str">
         <f>data!$E$44&amp;" "&amp;data!$B$44</f>
       </c>
-      <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool AD-2nd ",'Pool Matches'!O653)</f>
-      </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="20"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="20"/>
       <c r="I31" s="20"/>
     </row>
     <row r="32">
       <c r="A32" s="27" t="str">
         <f>data!$E$45&amp;" "&amp;data!$B$45</f>
       </c>
+      <c r="G32" s="21">
+        <v>36</v>
+      </c>
       <c r="H32" s="15"/>
       <c r="I32" s="20"/>
     </row>
     <row r="33">
       <c r="A33" s="22"/>
+      <c r="G33" s="20"/>
     </row>
     <row r="34">
       <c r="A34" s="24" t="str">
         <f>'data'!$A$48</f>
       </c>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23" t="str">
+        <f>CONCATENATE("Pool AD-2nd ",'Pool Matches'!O653)</f>
+      </c>
+      <c r="F34" s="15"/>
+      <c r="G34" s="20"/>
     </row>
     <row r="35">
       <c r="A35" s="25" t="str">

--- a/pools-example-large-teams.xlsx
+++ b/pools-example-large-teams.xlsx
@@ -21069,9 +21069,8 @@
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageSetup fitToHeight="0" fitToWidth="2" orientation="portrait" pageOrder="downThenOver" paperSize="9"/>
-  <rowBreaks count="16" manualBreakCount="16">
-    <brk id="1" max="16383" man="true"/>
-    <brk id="30" max="16383" man="true"/>
+  <rowBreaks count="15" manualBreakCount="15">
+    <brk id="34" max="16383" man="true"/>
     <brk id="54" max="16383" man="true"/>
     <brk id="97" max="16383" man="true"/>
     <brk id="140" max="16383" man="true"/>

--- a/pools-example-large-teams.xlsx
+++ b/pools-example-large-teams.xlsx
@@ -1294,94 +1294,94 @@
   </numFmts>
   <fonts count="13">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <u val="single"/>
+      <sz val="16"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color/>
-      <sz val="16"/>
-      <u val="single"/>
     </font>
     <font>
+      <b val="1"/>
+      <u val="single"/>
+      <sz val="12"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color/>
-      <sz val="12"/>
-      <u val="single"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color/>
-      <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="28"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="28"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="72"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="72"/>
     </font>
     <font>
+      <b val="1"/>
+      <i val="1"/>
+      <sz val="12"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <i val="1"/>
-      <color/>
-      <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="100"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="100"/>
     </font>
     <font>
+      <sz val="110"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="110"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="250"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color/>
-      <sz val="250"/>
     </font>
   </fonts>
   <fills count="6">
@@ -6081,16 +6081,16 @@
         <v>91</v>
       </c>
       <c r="D2" s="3">
-        <v>0.0020833333333333333</v>
+        <v>0.00208333333333333</v>
       </c>
       <c r="E2" s="3" t="str">
         <f>(A2*B2*C2*D2)</f>
       </c>
       <c r="F2" s="3">
-        <v>0.00034722222222222224</v>
+        <v>0.000347222222222222</v>
       </c>
       <c r="G2" s="3">
-        <v>0.020833333333333332</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="H2" s="31" t="str">
         <f>C2*I2+J2</f>
@@ -6107,16 +6107,16 @@
         <v>0</v>
       </c>
       <c r="D3" s="3">
-        <v>0.0020833333333333333</v>
+        <v>0.00208333333333333</v>
       </c>
       <c r="E3" s="3" t="str">
         <f>(A3*B3*C3*D3)</f>
       </c>
       <c r="F3" s="3">
-        <v>0.00034722222222222224</v>
+        <v>0.000347222222222222</v>
       </c>
       <c r="G3" s="3">
-        <v>0.020833333333333332</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="H3" s="3" t="str">
         <f>E3+(A3*C3*F3)+G3</f>
@@ -6185,16 +6185,16 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="3">
-        <v>0.002777777777777778</v>
+        <v>0.00277777777777777</v>
       </c>
       <c r="E8" s="3" t="str">
         <f>(A8*B8*D8)</f>
       </c>
       <c r="F8" s="3">
-        <v>0.00034722222222222224</v>
+        <v>0.000347222222222222</v>
       </c>
       <c r="G8" s="3">
-        <v>0.020833333333333332</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="H8" s="31" t="str">
         <f>E8+(A8*F8)+G8</f>
